--- a/sample_metadata.xlsx
+++ b/sample_metadata.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lukas\Documents\GitHub\btp_metagenomics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F5955A-424E-47D3-A525-21F41DFED59A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{923C5BC5-AFFE-4617-9D00-A387E38240C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -190,9 +190,6 @@
     <t>6/30/2021</t>
   </si>
   <si>
-    <t>1000198 - Mixed forest</t>
-  </si>
-  <si>
     <t>unknown</t>
   </si>
   <si>
@@ -226,9 +223,6 @@
     <t>3/26/2023</t>
   </si>
   <si>
-    <t>1000221 - Temperate woodland</t>
-  </si>
-  <si>
     <t>(DAD) Eucalyptus amygdalina forest and woodland on dolerite</t>
   </si>
   <si>
@@ -253,9 +247,6 @@
     <t>3/15/2022</t>
   </si>
   <si>
-    <t>1000218 - Xeric shrubland</t>
-  </si>
-  <si>
     <t>rocky</t>
   </si>
   <si>
@@ -298,9 +289,6 @@
     <t>SD02884</t>
   </si>
   <si>
-    <t>1000245 - Cropland</t>
-  </si>
-  <si>
     <t>EHI02796</t>
   </si>
   <si>
@@ -355,9 +343,6 @@
     <t>3/16/2023</t>
   </si>
   <si>
-    <t>1000215 - Temperate shrubland</t>
-  </si>
-  <si>
     <t>(SCH) Coastal heathland</t>
   </si>
   <si>
@@ -1322,6 +1307,21 @@
   </si>
   <si>
     <t>Site</t>
+  </si>
+  <si>
+    <t>Temperate woodland</t>
+  </si>
+  <si>
+    <t>Mixed forest</t>
+  </si>
+  <si>
+    <t>Cropland</t>
+  </si>
+  <si>
+    <t>Xeric shrubland</t>
+  </si>
+  <si>
+    <t>Temperate shrubland</t>
   </si>
 </sst>
 </file>
@@ -1681,6 +1681,7 @@
     <col min="10" max="10" width="18.85546875" customWidth="1"/>
     <col min="11" max="11" width="88.5703125" customWidth="1"/>
     <col min="12" max="12" width="18.85546875" customWidth="1"/>
+    <col min="36" max="36" width="31.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1718,7 +1719,7 @@
         <v>35</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>11</v>
@@ -1813,16 +1814,16 @@
     </row>
     <row r="2" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C2" t="s">
         <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E2" t="s">
         <v>45</v>
@@ -1831,7 +1832,7 @@
         <v>46</v>
       </c>
       <c r="G2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H2" t="s">
         <v>48</v>
@@ -1843,7 +1844,7 @@
         <v>147.97</v>
       </c>
       <c r="K2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -1873,40 +1874,40 @@
         <v>0.87709952882060505</v>
       </c>
       <c r="U2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="W2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="X2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="Y2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="Z2" t="s">
         <v>43</v>
       </c>
       <c r="AA2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="AB2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC2" t="s">
         <v>52</v>
       </c>
       <c r="AD2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE2" t="s">
         <v>65</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>66</v>
       </c>
       <c r="AF2">
         <v>2555</v>
       </c>
       <c r="AG2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="AH2">
         <v>9337</v>
@@ -1915,13 +1916,13 @@
         <v>9337</v>
       </c>
       <c r="AJ2" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK2">
         <v>84.61</v>
       </c>
       <c r="AL2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM2" t="s">
         <v>45</v>
@@ -1938,16 +1939,16 @@
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B3" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C3" t="s">
         <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E3" t="s">
         <v>45</v>
@@ -1968,7 +1969,7 @@
         <v>148.24</v>
       </c>
       <c r="K3" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -1998,31 +1999,31 @@
         <v>0.84151203670028696</v>
       </c>
       <c r="U3" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="W3" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="X3" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="Y3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="Z3" t="s">
         <v>43</v>
       </c>
       <c r="AA3" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="AB3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AC3" t="s">
         <v>52</v>
       </c>
       <c r="AD3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE3" t="s">
         <v>54</v>
@@ -2031,7 +2032,7 @@
         <v>3740</v>
       </c>
       <c r="AG3" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="AH3">
         <v>9337</v>
@@ -2040,13 +2041,13 @@
         <v>9337</v>
       </c>
       <c r="AJ3" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK3">
         <v>63.71</v>
       </c>
       <c r="AL3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM3" t="s">
         <v>45</v>
@@ -2063,16 +2064,16 @@
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" t="s">
         <v>59</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" t="s">
         <v>60</v>
-      </c>
-      <c r="C4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" t="s">
-        <v>61</v>
       </c>
       <c r="E4" t="s">
         <v>45</v>
@@ -2093,7 +2094,7 @@
         <v>146.21</v>
       </c>
       <c r="K4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="L4">
         <v>2</v>
@@ -2123,40 +2124,40 @@
         <v>0.85367449434436904</v>
       </c>
       <c r="U4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W4" t="s">
+        <v>59</v>
+      </c>
+      <c r="X4" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA4" t="s">
         <v>60</v>
       </c>
-      <c r="W4" t="s">
-        <v>60</v>
-      </c>
-      <c r="X4" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y4" t="s">
+      <c r="AB4" t="s">
         <v>63</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>64</v>
       </c>
       <c r="AC4" t="s">
         <v>52</v>
       </c>
       <c r="AD4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE4" t="s">
         <v>65</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>66</v>
       </c>
       <c r="AF4">
         <v>1475</v>
       </c>
       <c r="AG4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AH4">
         <v>9337</v>
@@ -2165,13 +2166,13 @@
         <v>9337</v>
       </c>
       <c r="AJ4" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK4">
         <v>69.150000000000006</v>
       </c>
       <c r="AL4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM4" t="s">
         <v>45</v>
@@ -2188,16 +2189,16 @@
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B5" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C5" t="s">
         <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
         <v>45</v>
@@ -2218,7 +2219,7 @@
         <v>146.21</v>
       </c>
       <c r="K5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="L5">
         <v>2</v>
@@ -2248,31 +2249,31 @@
         <v>0.85032448979825304</v>
       </c>
       <c r="U5" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="W5" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="X5" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="Y5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="Z5" t="s">
         <v>43</v>
       </c>
       <c r="AA5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AB5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC5" t="s">
         <v>52</v>
       </c>
       <c r="AD5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE5" t="s">
         <v>54</v>
@@ -2281,7 +2282,7 @@
         <v>2850</v>
       </c>
       <c r="AG5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="AH5">
         <v>9337</v>
@@ -2290,13 +2291,13 @@
         <v>9337</v>
       </c>
       <c r="AJ5" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK5">
         <v>70.17</v>
       </c>
       <c r="AL5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM5" t="s">
         <v>45</v>
@@ -2313,16 +2314,16 @@
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B6" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C6" t="s">
         <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
         <v>45</v>
@@ -2331,7 +2332,7 @@
         <v>46</v>
       </c>
       <c r="G6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H6" t="s">
         <v>48</v>
@@ -2343,7 +2344,7 @@
         <v>146.21</v>
       </c>
       <c r="K6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -2373,31 +2374,31 @@
         <v>0.84460527127034302</v>
       </c>
       <c r="U6" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="W6" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="X6" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="Y6" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="Z6" t="s">
         <v>43</v>
       </c>
       <c r="AA6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AB6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC6" t="s">
         <v>52</v>
       </c>
       <c r="AD6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE6" t="s">
         <v>54</v>
@@ -2406,7 +2407,7 @@
         <v>3100</v>
       </c>
       <c r="AG6" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="AH6">
         <v>9337</v>
@@ -2415,13 +2416,13 @@
         <v>9337</v>
       </c>
       <c r="AJ6" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK6">
         <v>73.08</v>
       </c>
       <c r="AL6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM6" t="s">
         <v>45</v>
@@ -2438,16 +2439,16 @@
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="B7" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="C7" t="s">
         <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
         <v>45</v>
@@ -2468,7 +2469,7 @@
         <v>146.21</v>
       </c>
       <c r="K7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="L7">
         <v>2</v>
@@ -2498,40 +2499,40 @@
         <v>0.86098268871805195</v>
       </c>
       <c r="U7" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="W7" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="X7" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="Y7" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="Z7" t="s">
         <v>43</v>
       </c>
       <c r="AA7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AB7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AC7" t="s">
         <v>52</v>
       </c>
       <c r="AD7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE7" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="AF7">
         <v>1350</v>
       </c>
       <c r="AG7" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="AH7">
         <v>9337</v>
@@ -2540,13 +2541,13 @@
         <v>9337</v>
       </c>
       <c r="AJ7" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK7">
         <v>67.59</v>
       </c>
       <c r="AL7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM7" t="s">
         <v>45</v>
@@ -2563,16 +2564,16 @@
     </row>
     <row r="8" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B8" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C8" t="s">
         <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E8" t="s">
         <v>45</v>
@@ -2581,7 +2582,7 @@
         <v>46</v>
       </c>
       <c r="G8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H8" t="s">
         <v>48</v>
@@ -2593,7 +2594,7 @@
         <v>146.72</v>
       </c>
       <c r="K8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="L8">
         <v>2</v>
@@ -2623,31 +2624,31 @@
         <v>0.832532806817744</v>
       </c>
       <c r="U8" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="W8" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="X8" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="Y8" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="Z8" t="s">
         <v>43</v>
       </c>
       <c r="AA8" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="AB8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC8" t="s">
         <v>52</v>
       </c>
       <c r="AD8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE8" t="s">
         <v>54</v>
@@ -2656,7 +2657,7 @@
         <v>2880</v>
       </c>
       <c r="AG8" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="AH8">
         <v>9337</v>
@@ -2665,13 +2666,13 @@
         <v>9337</v>
       </c>
       <c r="AJ8" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK8">
         <v>73.959999999999994</v>
       </c>
       <c r="AL8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM8" t="s">
         <v>45</v>
@@ -2688,16 +2689,16 @@
     </row>
     <row r="9" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
         <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E9" t="s">
         <v>45</v>
@@ -2706,7 +2707,7 @@
         <v>46</v>
       </c>
       <c r="G9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H9" t="s">
         <v>48</v>
@@ -2718,7 +2719,7 @@
         <v>147.32</v>
       </c>
       <c r="K9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L9">
         <v>3</v>
@@ -2748,31 +2749,31 @@
         <v>0.88863280943404399</v>
       </c>
       <c r="U9" t="s">
+        <v>77</v>
+      </c>
+      <c r="W9" t="s">
+        <v>77</v>
+      </c>
+      <c r="X9" t="s">
         <v>80</v>
       </c>
-      <c r="W9" t="s">
-        <v>80</v>
-      </c>
-      <c r="X9" t="s">
-        <v>83</v>
-      </c>
       <c r="Y9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Z9" t="s">
         <v>43</v>
       </c>
       <c r="AA9" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="AB9" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC9" t="s">
         <v>52</v>
       </c>
       <c r="AD9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE9" t="s">
         <v>54</v>
@@ -2781,7 +2782,7 @@
         <v>2925</v>
       </c>
       <c r="AG9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="AH9">
         <v>9337</v>
@@ -2790,13 +2791,13 @@
         <v>9337</v>
       </c>
       <c r="AJ9" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK9">
         <v>69.09</v>
       </c>
       <c r="AL9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM9" t="s">
         <v>45</v>
@@ -2813,16 +2814,16 @@
     </row>
     <row r="10" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B10" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C10" t="s">
         <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E10" t="s">
         <v>45</v>
@@ -2831,7 +2832,7 @@
         <v>46</v>
       </c>
       <c r="G10" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H10" t="s">
         <v>48</v>
@@ -2843,7 +2844,7 @@
         <v>147.32</v>
       </c>
       <c r="K10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L10">
         <v>3</v>
@@ -2873,31 +2874,31 @@
         <v>0.83384400465743402</v>
       </c>
       <c r="U10" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="W10" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="X10" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="Y10" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="Z10" t="s">
         <v>43</v>
       </c>
       <c r="AA10" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="AB10" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC10" t="s">
         <v>52</v>
       </c>
       <c r="AD10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE10" t="s">
         <v>54</v>
@@ -2906,7 +2907,7 @@
         <v>1800</v>
       </c>
       <c r="AG10" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="AH10">
         <v>9337</v>
@@ -2915,13 +2916,13 @@
         <v>9337</v>
       </c>
       <c r="AJ10" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK10">
         <v>76.209999999999994</v>
       </c>
       <c r="AL10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM10" t="s">
         <v>45</v>
@@ -2938,16 +2939,16 @@
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="B11" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C11" t="s">
         <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E11" t="s">
         <v>45</v>
@@ -2956,7 +2957,7 @@
         <v>46</v>
       </c>
       <c r="G11" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s">
         <v>48</v>
@@ -2968,7 +2969,7 @@
         <v>147.32</v>
       </c>
       <c r="K11" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L11">
         <v>3</v>
@@ -2998,31 +2999,31 @@
         <v>0.85790431504485398</v>
       </c>
       <c r="U11" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="W11" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="X11" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="Y11" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="Z11" t="s">
         <v>43</v>
       </c>
       <c r="AA11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="AB11" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC11" t="s">
         <v>52</v>
       </c>
       <c r="AD11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE11" t="s">
         <v>54</v>
@@ -3031,7 +3032,7 @@
         <v>2150</v>
       </c>
       <c r="AG11" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="AH11">
         <v>9337</v>
@@ -3040,13 +3041,13 @@
         <v>9337</v>
       </c>
       <c r="AJ11" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK11">
         <v>70.5</v>
       </c>
       <c r="AL11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM11" t="s">
         <v>45</v>
@@ -3063,16 +3064,16 @@
     </row>
     <row r="12" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B12" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C12" t="s">
         <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E12" t="s">
         <v>45</v>
@@ -3081,7 +3082,7 @@
         <v>46</v>
       </c>
       <c r="G12" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s">
         <v>48</v>
@@ -3093,7 +3094,7 @@
         <v>147.24</v>
       </c>
       <c r="K12" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L12">
         <v>3</v>
@@ -3123,31 +3124,31 @@
         <v>0.78431847471945004</v>
       </c>
       <c r="U12" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="W12" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="X12" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="Y12" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="Z12" t="s">
         <v>43</v>
       </c>
       <c r="AA12" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="AB12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC12" t="s">
         <v>52</v>
       </c>
       <c r="AD12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE12" t="s">
         <v>54</v>
@@ -3156,7 +3157,7 @@
         <v>1925</v>
       </c>
       <c r="AG12" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="AH12">
         <v>9337</v>
@@ -3165,13 +3166,13 @@
         <v>9337</v>
       </c>
       <c r="AJ12" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK12">
         <v>60.68</v>
       </c>
       <c r="AL12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM12" t="s">
         <v>45</v>
@@ -3188,16 +3189,16 @@
     </row>
     <row r="13" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="B13" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="C13" t="s">
         <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
         <v>45</v>
@@ -3206,7 +3207,7 @@
         <v>46</v>
       </c>
       <c r="G13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s">
         <v>48</v>
@@ -3218,7 +3219,7 @@
         <v>147.96</v>
       </c>
       <c r="K13" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="L13">
         <v>4</v>
@@ -3248,31 +3249,31 @@
         <v>0.91450630850145598</v>
       </c>
       <c r="U13" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="W13" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="X13" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="Y13" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="Z13" t="s">
         <v>43</v>
       </c>
       <c r="AA13" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="AB13" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC13" t="s">
         <v>52</v>
       </c>
       <c r="AD13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE13" t="s">
         <v>54</v>
@@ -3281,7 +3282,7 @@
         <v>3055</v>
       </c>
       <c r="AG13" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="AH13">
         <v>9337</v>
@@ -3290,13 +3291,13 @@
         <v>9337</v>
       </c>
       <c r="AJ13" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK13">
         <v>68.47</v>
       </c>
       <c r="AL13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM13" t="s">
         <v>45</v>
@@ -3313,16 +3314,16 @@
     </row>
     <row r="14" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B14" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C14" t="s">
         <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E14" t="s">
         <v>45</v>
@@ -3343,7 +3344,7 @@
         <v>147.96</v>
       </c>
       <c r="K14" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="L14">
         <v>4</v>
@@ -3373,31 +3374,31 @@
         <v>0.89019477469939301</v>
       </c>
       <c r="U14" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="W14" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="X14" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="Y14" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="Z14" t="s">
         <v>43</v>
       </c>
       <c r="AA14" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="AB14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC14" t="s">
         <v>52</v>
       </c>
       <c r="AD14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE14" t="s">
         <v>54</v>
@@ -3406,7 +3407,7 @@
         <v>3400</v>
       </c>
       <c r="AG14" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="AH14">
         <v>9337</v>
@@ -3415,13 +3416,13 @@
         <v>9337</v>
       </c>
       <c r="AJ14" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK14">
         <v>76.56</v>
       </c>
       <c r="AL14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM14" t="s">
         <v>45</v>
@@ -3438,16 +3439,16 @@
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B15" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C15" t="s">
         <v>43</v>
       </c>
       <c r="D15" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E15" t="s">
         <v>45</v>
@@ -3468,7 +3469,7 @@
         <v>148.27000000000001</v>
       </c>
       <c r="K15" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="L15">
         <v>5</v>
@@ -3498,40 +3499,40 @@
         <v>0.81545080741082399</v>
       </c>
       <c r="U15" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="W15" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="X15" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="Y15" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="Z15" t="s">
         <v>43</v>
       </c>
       <c r="AA15" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="AB15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AC15" t="s">
         <v>52</v>
       </c>
       <c r="AD15" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE15" t="s">
         <v>65</v>
-      </c>
-      <c r="AE15" t="s">
-        <v>66</v>
       </c>
       <c r="AF15">
         <v>2050</v>
       </c>
       <c r="AG15" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="AH15">
         <v>9337</v>
@@ -3540,13 +3541,13 @@
         <v>9337</v>
       </c>
       <c r="AJ15" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK15">
         <v>74.349999999999994</v>
       </c>
       <c r="AL15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM15" t="s">
         <v>45</v>
@@ -3563,16 +3564,16 @@
     </row>
     <row r="16" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B16" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C16" t="s">
         <v>43</v>
       </c>
       <c r="D16" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E16" t="s">
         <v>45</v>
@@ -3581,7 +3582,7 @@
         <v>46</v>
       </c>
       <c r="G16" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s">
         <v>48</v>
@@ -3593,7 +3594,7 @@
         <v>148.27000000000001</v>
       </c>
       <c r="K16" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="L16">
         <v>5</v>
@@ -3623,31 +3624,31 @@
         <v>0.71673885087940403</v>
       </c>
       <c r="U16" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="W16" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="X16" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="Y16" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z16" t="s">
         <v>43</v>
       </c>
       <c r="AA16" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="AB16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AC16" t="s">
         <v>52</v>
       </c>
       <c r="AD16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE16" t="s">
         <v>54</v>
@@ -3656,7 +3657,7 @@
         <v>4660</v>
       </c>
       <c r="AG16" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="AH16">
         <v>9337</v>
@@ -3665,13 +3666,13 @@
         <v>9337</v>
       </c>
       <c r="AJ16" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK16">
         <v>71.510000000000005</v>
       </c>
       <c r="AL16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM16" t="s">
         <v>45</v>
@@ -3688,16 +3689,16 @@
     </row>
     <row r="17" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B17" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C17" t="s">
         <v>43</v>
       </c>
       <c r="D17" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E17" t="s">
         <v>45</v>
@@ -3706,7 +3707,7 @@
         <v>46</v>
       </c>
       <c r="G17" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s">
         <v>48</v>
@@ -3718,7 +3719,7 @@
         <v>147.97</v>
       </c>
       <c r="K17" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="L17">
         <v>6</v>
@@ -3748,31 +3749,31 @@
         <v>0.87960716507236203</v>
       </c>
       <c r="U17" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="W17" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="X17" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Y17" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="Z17" t="s">
         <v>43</v>
       </c>
       <c r="AA17" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="AB17" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC17" t="s">
         <v>52</v>
       </c>
       <c r="AD17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE17" t="s">
         <v>54</v>
@@ -3781,7 +3782,7 @@
         <v>3600</v>
       </c>
       <c r="AG17" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="AH17">
         <v>9337</v>
@@ -3790,13 +3791,13 @@
         <v>9337</v>
       </c>
       <c r="AJ17" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK17">
         <v>73.989999999999995</v>
       </c>
       <c r="AL17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM17" t="s">
         <v>45</v>
@@ -3813,16 +3814,16 @@
     </row>
     <row r="18" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B18" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C18" t="s">
         <v>43</v>
       </c>
       <c r="D18" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E18" t="s">
         <v>45</v>
@@ -3843,7 +3844,7 @@
         <v>147.13999999999999</v>
       </c>
       <c r="K18" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="L18">
         <v>7</v>
@@ -3873,31 +3874,31 @@
         <v>0.79279665935218302</v>
       </c>
       <c r="U18" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="W18" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="X18" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="Y18" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="Z18" t="s">
         <v>43</v>
       </c>
       <c r="AA18" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="AB18" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC18" t="s">
         <v>52</v>
       </c>
       <c r="AD18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE18" t="s">
         <v>54</v>
@@ -3906,7 +3907,7 @@
         <v>2300</v>
       </c>
       <c r="AG18" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="AH18">
         <v>9337</v>
@@ -3915,13 +3916,13 @@
         <v>9337</v>
       </c>
       <c r="AJ18" t="s">
-        <v>92</v>
+        <v>431</v>
       </c>
       <c r="AK18">
         <v>75.72</v>
       </c>
       <c r="AL18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM18" t="s">
         <v>45</v>
@@ -3938,16 +3939,16 @@
     </row>
     <row r="19" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="B19" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="C19" t="s">
         <v>43</v>
       </c>
       <c r="D19" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E19" t="s">
         <v>45</v>
@@ -3956,7 +3957,7 @@
         <v>46</v>
       </c>
       <c r="G19" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H19" t="s">
         <v>48</v>
@@ -3968,7 +3969,7 @@
         <v>147.13999999999999</v>
       </c>
       <c r="K19" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="L19">
         <v>7</v>
@@ -3998,37 +3999,37 @@
         <v>0.81754712567711096</v>
       </c>
       <c r="U19" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="W19" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="X19" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="Y19" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="Z19" t="s">
         <v>43</v>
       </c>
       <c r="AA19" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="AB19" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC19" t="s">
         <v>52</v>
       </c>
       <c r="AD19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE19" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AG19" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="AH19">
         <v>9337</v>
@@ -4037,13 +4038,13 @@
         <v>9337</v>
       </c>
       <c r="AJ19" t="s">
-        <v>92</v>
+        <v>431</v>
       </c>
       <c r="AK19">
         <v>59.79</v>
       </c>
       <c r="AL19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM19" t="s">
         <v>45</v>
@@ -4060,16 +4061,16 @@
     </row>
     <row r="20" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="B20" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C20" t="s">
         <v>43</v>
       </c>
       <c r="D20" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E20" t="s">
         <v>45</v>
@@ -4078,7 +4079,7 @@
         <v>46</v>
       </c>
       <c r="G20" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s">
         <v>48</v>
@@ -4090,7 +4091,7 @@
         <v>147.13999999999999</v>
       </c>
       <c r="K20" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="L20">
         <v>7</v>
@@ -4120,31 +4121,31 @@
         <v>0.80368336060573797</v>
       </c>
       <c r="U20" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="W20" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="X20" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="Y20" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="Z20" t="s">
         <v>43</v>
       </c>
       <c r="AA20" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="AB20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AC20" t="s">
         <v>52</v>
       </c>
       <c r="AD20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE20" t="s">
         <v>54</v>
@@ -4153,7 +4154,7 @@
         <v>4300</v>
       </c>
       <c r="AG20" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="AH20">
         <v>9337</v>
@@ -4162,13 +4163,13 @@
         <v>9337</v>
       </c>
       <c r="AJ20" t="s">
-        <v>92</v>
+        <v>431</v>
       </c>
       <c r="AK20">
         <v>77.42</v>
       </c>
       <c r="AL20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM20" t="s">
         <v>45</v>
@@ -4185,16 +4186,16 @@
     </row>
     <row r="21" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C21" t="s">
         <v>43</v>
       </c>
       <c r="D21" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E21" t="s">
         <v>45</v>
@@ -4215,7 +4216,7 @@
         <v>147.71</v>
       </c>
       <c r="K21" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="L21">
         <v>7</v>
@@ -4245,31 +4246,31 @@
         <v>0.786656206045657</v>
       </c>
       <c r="U21" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="W21" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="X21" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="Y21" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="Z21" t="s">
         <v>43</v>
       </c>
       <c r="AA21" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="AB21" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC21" t="s">
         <v>52</v>
       </c>
       <c r="AD21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE21" t="s">
         <v>54</v>
@@ -4278,7 +4279,7 @@
         <v>2980</v>
       </c>
       <c r="AG21" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="AH21">
         <v>9337</v>
@@ -4287,13 +4288,13 @@
         <v>9337</v>
       </c>
       <c r="AJ21" t="s">
-        <v>92</v>
+        <v>431</v>
       </c>
       <c r="AK21">
         <v>70.489999999999995</v>
       </c>
       <c r="AL21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM21" t="s">
         <v>45</v>
@@ -4310,16 +4311,16 @@
     </row>
     <row r="22" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B22" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C22" t="s">
         <v>43</v>
       </c>
       <c r="D22" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E22" t="s">
         <v>45</v>
@@ -4328,7 +4329,7 @@
         <v>46</v>
       </c>
       <c r="G22" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H22" t="s">
         <v>48</v>
@@ -4340,7 +4341,7 @@
         <v>145.4</v>
       </c>
       <c r="K22" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="L22">
         <v>7</v>
@@ -4370,37 +4371,37 @@
         <v>0.74490721202742105</v>
       </c>
       <c r="U22" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="W22" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="X22" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="Y22" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="Z22" t="s">
         <v>43</v>
       </c>
       <c r="AA22" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="AB22" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC22" t="s">
         <v>52</v>
       </c>
       <c r="AD22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE22" t="s">
         <v>54</v>
       </c>
       <c r="AG22" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="AH22">
         <v>9337</v>
@@ -4409,13 +4410,13 @@
         <v>9337</v>
       </c>
       <c r="AJ22" t="s">
-        <v>92</v>
+        <v>431</v>
       </c>
       <c r="AK22">
         <v>71.59</v>
       </c>
       <c r="AL22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM22" t="s">
         <v>45</v>
@@ -4432,16 +4433,16 @@
     </row>
     <row r="23" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B23" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C23" t="s">
         <v>43</v>
       </c>
       <c r="D23" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E23" t="s">
         <v>45</v>
@@ -4450,7 +4451,7 @@
         <v>46</v>
       </c>
       <c r="G23" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H23" t="s">
         <v>48</v>
@@ -4462,7 +4463,7 @@
         <v>147.69999999999999</v>
       </c>
       <c r="K23" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="L23">
         <v>8</v>
@@ -4492,40 +4493,40 @@
         <v>0.75467476651543397</v>
       </c>
       <c r="U23" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="W23" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="X23" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="Y23" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="Z23" t="s">
         <v>43</v>
       </c>
       <c r="AA23" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="AB23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AC23" t="s">
         <v>52</v>
       </c>
       <c r="AD23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE23" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AF23">
         <v>3665</v>
       </c>
       <c r="AG23" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AH23">
         <v>9337</v>
@@ -4534,13 +4535,13 @@
         <v>9337</v>
       </c>
       <c r="AJ23" t="s">
-        <v>92</v>
+        <v>431</v>
       </c>
       <c r="AK23">
         <v>74.010000000000005</v>
       </c>
       <c r="AL23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM23" t="s">
         <v>45</v>
@@ -4557,16 +4558,16 @@
     </row>
     <row r="24" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B24" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C24" t="s">
         <v>43</v>
       </c>
       <c r="D24" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E24" t="s">
         <v>45</v>
@@ -4575,7 +4576,7 @@
         <v>46</v>
       </c>
       <c r="G24" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s">
         <v>48</v>
@@ -4587,7 +4588,7 @@
         <v>147.69999999999999</v>
       </c>
       <c r="K24" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L24">
         <v>8</v>
@@ -4617,31 +4618,31 @@
         <v>0.72325340741730704</v>
       </c>
       <c r="U24" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="W24" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="X24" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="Y24" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="Z24" t="s">
         <v>43</v>
       </c>
       <c r="AA24" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="AB24" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC24" t="s">
         <v>52</v>
       </c>
       <c r="AD24" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE24" t="s">
         <v>54</v>
@@ -4650,7 +4651,7 @@
         <v>3670</v>
       </c>
       <c r="AG24" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="AH24">
         <v>9337</v>
@@ -4659,13 +4660,13 @@
         <v>9337</v>
       </c>
       <c r="AJ24" t="s">
-        <v>92</v>
+        <v>431</v>
       </c>
       <c r="AK24">
         <v>77.05</v>
       </c>
       <c r="AL24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM24" t="s">
         <v>45</v>
@@ -4682,16 +4683,16 @@
     </row>
     <row r="25" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B25" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C25" t="s">
         <v>43</v>
       </c>
       <c r="D25" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E25" t="s">
         <v>45</v>
@@ -4712,7 +4713,7 @@
         <v>146.24</v>
       </c>
       <c r="K25" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="L25">
         <v>9</v>
@@ -4742,31 +4743,31 @@
         <v>0.75314467877064895</v>
       </c>
       <c r="U25" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="W25" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="X25" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="Y25" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="Z25" t="s">
         <v>43</v>
       </c>
       <c r="AA25" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="AB25" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC25" t="s">
         <v>52</v>
       </c>
       <c r="AD25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE25" t="s">
         <v>54</v>
@@ -4775,7 +4776,7 @@
         <v>3700</v>
       </c>
       <c r="AG25" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="AH25">
         <v>9337</v>
@@ -4784,13 +4785,13 @@
         <v>9337</v>
       </c>
       <c r="AJ25" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK25">
         <v>62.24</v>
       </c>
       <c r="AL25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM25" t="s">
         <v>45</v>
@@ -4807,16 +4808,16 @@
     </row>
     <row r="26" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B26" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C26" t="s">
         <v>43</v>
       </c>
       <c r="D26" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E26" t="s">
         <v>45</v>
@@ -4825,7 +4826,7 @@
         <v>46</v>
       </c>
       <c r="G26" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s">
         <v>48</v>
@@ -4837,7 +4838,7 @@
         <v>145.6</v>
       </c>
       <c r="K26" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="L26">
         <v>10</v>
@@ -4867,31 +4868,31 @@
         <v>0.85795068378238903</v>
       </c>
       <c r="U26" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="W26" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="X26" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="Y26" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="Z26" t="s">
         <v>43</v>
       </c>
       <c r="AA26" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="AB26" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC26" t="s">
         <v>52</v>
       </c>
       <c r="AD26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE26" t="s">
         <v>54</v>
@@ -4900,7 +4901,7 @@
         <v>3750</v>
       </c>
       <c r="AG26" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="AH26">
         <v>9337</v>
@@ -4909,13 +4910,13 @@
         <v>9337</v>
       </c>
       <c r="AJ26" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK26">
         <v>67.010000000000005</v>
       </c>
       <c r="AL26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM26" t="s">
         <v>45</v>
@@ -4932,16 +4933,16 @@
     </row>
     <row r="27" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C27" t="s">
         <v>43</v>
       </c>
       <c r="D27" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E27" t="s">
         <v>45</v>
@@ -4950,7 +4951,7 @@
         <v>46</v>
       </c>
       <c r="G27" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s">
         <v>48</v>
@@ -4962,7 +4963,7 @@
         <v>145.6</v>
       </c>
       <c r="K27" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="L27">
         <v>10</v>
@@ -4992,31 +4993,31 @@
         <v>0.77041877448982499</v>
       </c>
       <c r="U27" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="W27" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="X27" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="Y27" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="Z27" t="s">
         <v>43</v>
       </c>
       <c r="AA27" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="AB27" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC27" t="s">
         <v>52</v>
       </c>
       <c r="AD27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE27" t="s">
         <v>54</v>
@@ -5025,7 +5026,7 @@
         <v>3650</v>
       </c>
       <c r="AG27" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="AH27">
         <v>9337</v>
@@ -5034,13 +5035,13 @@
         <v>9337</v>
       </c>
       <c r="AJ27" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK27">
         <v>70.67</v>
       </c>
       <c r="AL27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM27" t="s">
         <v>45</v>
@@ -5057,16 +5058,16 @@
     </row>
     <row r="28" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B28" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C28" t="s">
         <v>43</v>
       </c>
       <c r="D28" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E28" t="s">
         <v>45</v>
@@ -5087,7 +5088,7 @@
         <v>145.6</v>
       </c>
       <c r="K28" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="L28">
         <v>10</v>
@@ -5117,31 +5118,31 @@
         <v>0.84238531005911399</v>
       </c>
       <c r="U28" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="W28" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="X28" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="Y28" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="Z28" t="s">
         <v>43</v>
       </c>
       <c r="AA28" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="AB28" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC28" t="s">
         <v>52</v>
       </c>
       <c r="AD28" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE28" t="s">
         <v>54</v>
@@ -5150,7 +5151,7 @@
         <v>4050</v>
       </c>
       <c r="AG28" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="AH28">
         <v>9337</v>
@@ -5159,13 +5160,13 @@
         <v>9337</v>
       </c>
       <c r="AJ28" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK28">
         <v>74.34</v>
       </c>
       <c r="AL28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM28" t="s">
         <v>45</v>
@@ -5182,16 +5183,16 @@
     </row>
     <row r="29" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="B29" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="C29" t="s">
         <v>43</v>
       </c>
       <c r="D29" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E29" t="s">
         <v>45</v>
@@ -5200,7 +5201,7 @@
         <v>46</v>
       </c>
       <c r="G29" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s">
         <v>48</v>
@@ -5212,7 +5213,7 @@
         <v>145.61000000000001</v>
       </c>
       <c r="K29" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="L29">
         <v>10</v>
@@ -5242,40 +5243,40 @@
         <v>0.80978355201659202</v>
       </c>
       <c r="U29" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="W29" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="X29" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="Y29" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="Z29" t="s">
         <v>43</v>
       </c>
       <c r="AA29" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="AB29" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC29" t="s">
         <v>52</v>
       </c>
       <c r="AD29" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE29" t="s">
         <v>65</v>
-      </c>
-      <c r="AE29" t="s">
-        <v>66</v>
       </c>
       <c r="AF29">
         <v>2100</v>
       </c>
       <c r="AG29" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="AH29">
         <v>9337</v>
@@ -5284,13 +5285,13 @@
         <v>9337</v>
       </c>
       <c r="AJ29" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK29">
         <v>61.49</v>
       </c>
       <c r="AL29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM29" t="s">
         <v>45</v>
@@ -5307,16 +5308,16 @@
     </row>
     <row r="30" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B30" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="C30" t="s">
         <v>43</v>
       </c>
       <c r="D30" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E30" t="s">
         <v>45</v>
@@ -5337,7 +5338,7 @@
         <v>145.6</v>
       </c>
       <c r="K30" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="L30">
         <v>10</v>
@@ -5367,31 +5368,31 @@
         <v>0.84762316796249204</v>
       </c>
       <c r="U30" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="W30" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="X30" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="Y30" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="Z30" t="s">
         <v>43</v>
       </c>
       <c r="AA30" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="AB30" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC30" t="s">
         <v>52</v>
       </c>
       <c r="AD30" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE30" t="s">
         <v>54</v>
@@ -5400,7 +5401,7 @@
         <v>3450</v>
       </c>
       <c r="AG30" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="AH30">
         <v>9337</v>
@@ -5409,13 +5410,13 @@
         <v>9337</v>
       </c>
       <c r="AJ30" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK30">
         <v>70.58</v>
       </c>
       <c r="AL30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM30" t="s">
         <v>45</v>
@@ -5432,16 +5433,16 @@
     </row>
     <row r="31" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B31" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C31" t="s">
         <v>43</v>
       </c>
       <c r="D31" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E31" t="s">
         <v>45</v>
@@ -5450,7 +5451,7 @@
         <v>46</v>
       </c>
       <c r="G31" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s">
         <v>48</v>
@@ -5462,7 +5463,7 @@
         <v>146.72</v>
       </c>
       <c r="K31" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="L31">
         <v>11</v>
@@ -5492,40 +5493,40 @@
         <v>0.80510152896000298</v>
       </c>
       <c r="U31" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="W31" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="X31" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="Y31" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="Z31" t="s">
         <v>43</v>
       </c>
       <c r="AA31" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="AB31" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC31" t="s">
         <v>52</v>
       </c>
       <c r="AD31" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE31" t="s">
         <v>65</v>
-      </c>
-      <c r="AE31" t="s">
-        <v>66</v>
       </c>
       <c r="AF31">
         <v>1260</v>
       </c>
       <c r="AG31" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="AH31">
         <v>9337</v>
@@ -5534,13 +5535,13 @@
         <v>9337</v>
       </c>
       <c r="AJ31" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK31">
         <v>68.08</v>
       </c>
       <c r="AL31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM31" t="s">
         <v>45</v>
@@ -5557,16 +5558,16 @@
     </row>
     <row r="32" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="B32" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="C32" t="s">
         <v>43</v>
       </c>
       <c r="D32" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E32" t="s">
         <v>45</v>
@@ -5575,7 +5576,7 @@
         <v>46</v>
       </c>
       <c r="G32" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s">
         <v>48</v>
@@ -5587,7 +5588,7 @@
         <v>146.72</v>
       </c>
       <c r="K32" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="L32">
         <v>11</v>
@@ -5617,31 +5618,31 @@
         <v>0.76757042024279698</v>
       </c>
       <c r="U32" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="W32" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="X32" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="Y32" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="Z32" t="s">
         <v>43</v>
       </c>
       <c r="AA32" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="AB32" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC32" t="s">
         <v>52</v>
       </c>
       <c r="AD32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE32" t="s">
         <v>54</v>
@@ -5650,7 +5651,7 @@
         <v>2740</v>
       </c>
       <c r="AG32" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="AH32">
         <v>9337</v>
@@ -5659,13 +5660,13 @@
         <v>9337</v>
       </c>
       <c r="AJ32" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK32">
         <v>71.55</v>
       </c>
       <c r="AL32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM32" t="s">
         <v>45</v>
@@ -5682,16 +5683,16 @@
     </row>
     <row r="33" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B33" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C33" t="s">
         <v>43</v>
       </c>
       <c r="D33" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E33" t="s">
         <v>45</v>
@@ -5700,7 +5701,7 @@
         <v>46</v>
       </c>
       <c r="G33" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s">
         <v>48</v>
@@ -5712,7 +5713,7 @@
         <v>145.47999999999999</v>
       </c>
       <c r="K33" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="L33">
         <v>12</v>
@@ -5742,31 +5743,31 @@
         <v>0.64863036047171296</v>
       </c>
       <c r="U33" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="W33" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="X33" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="Y33" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="Z33" t="s">
         <v>43</v>
       </c>
       <c r="AA33" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="AB33" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC33" t="s">
         <v>52</v>
       </c>
       <c r="AD33" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE33" t="s">
         <v>54</v>
@@ -5775,7 +5776,7 @@
         <v>3900</v>
       </c>
       <c r="AG33" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="AH33">
         <v>9337</v>
@@ -5784,13 +5785,13 @@
         <v>9337</v>
       </c>
       <c r="AJ33" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK33">
         <v>73.55</v>
       </c>
       <c r="AL33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM33" t="s">
         <v>45</v>
@@ -5807,16 +5808,16 @@
     </row>
     <row r="34" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B34" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C34" t="s">
         <v>43</v>
       </c>
       <c r="D34" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E34" t="s">
         <v>45</v>
@@ -5837,7 +5838,7 @@
         <v>145.47999999999999</v>
       </c>
       <c r="K34" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="L34">
         <v>12</v>
@@ -5867,37 +5868,37 @@
         <v>0.78520688963351604</v>
       </c>
       <c r="U34" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="W34" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="X34" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="Y34" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="Z34" t="s">
         <v>43</v>
       </c>
       <c r="AA34" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="AB34" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC34" t="s">
         <v>52</v>
       </c>
       <c r="AD34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE34" t="s">
         <v>54</v>
       </c>
       <c r="AG34" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="AH34">
         <v>9337</v>
@@ -5906,13 +5907,13 @@
         <v>9337</v>
       </c>
       <c r="AJ34" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK34">
         <v>68.08</v>
       </c>
       <c r="AL34" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM34" t="s">
         <v>45</v>
@@ -5929,16 +5930,16 @@
     </row>
     <row r="35" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="B35" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="C35" t="s">
         <v>43</v>
       </c>
       <c r="D35" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E35" t="s">
         <v>45</v>
@@ -5947,7 +5948,7 @@
         <v>46</v>
       </c>
       <c r="G35" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s">
         <v>48</v>
@@ -5959,7 +5960,7 @@
         <v>145.47999999999999</v>
       </c>
       <c r="K35" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="L35">
         <v>12</v>
@@ -5989,37 +5990,37 @@
         <v>0.84538537843579697</v>
       </c>
       <c r="U35" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="W35" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="X35" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="Y35" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="Z35" t="s">
         <v>43</v>
       </c>
       <c r="AA35" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="AB35" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC35" t="s">
         <v>52</v>
       </c>
       <c r="AD35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE35" t="s">
         <v>54</v>
       </c>
       <c r="AG35" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="AH35">
         <v>9337</v>
@@ -6028,13 +6029,13 @@
         <v>9337</v>
       </c>
       <c r="AJ35" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK35">
         <v>60.51</v>
       </c>
       <c r="AL35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM35" t="s">
         <v>45</v>
@@ -6051,16 +6052,16 @@
     </row>
     <row r="36" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B36" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C36" t="s">
         <v>43</v>
       </c>
       <c r="D36" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E36" t="s">
         <v>45</v>
@@ -6081,7 +6082,7 @@
         <v>147.69999999999999</v>
       </c>
       <c r="K36" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="L36">
         <v>13</v>
@@ -6111,31 +6112,31 @@
         <v>0.71967155814418504</v>
       </c>
       <c r="U36" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="W36" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="X36" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="Y36" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="Z36" t="s">
         <v>43</v>
       </c>
       <c r="AA36" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="AB36" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC36" t="s">
         <v>52</v>
       </c>
       <c r="AD36" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE36" t="s">
         <v>54</v>
@@ -6144,7 +6145,7 @@
         <v>3670</v>
       </c>
       <c r="AG36" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AH36">
         <v>9337</v>
@@ -6153,13 +6154,13 @@
         <v>9337</v>
       </c>
       <c r="AJ36" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK36">
         <v>73.37</v>
       </c>
       <c r="AL36" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM36" t="s">
         <v>45</v>
@@ -6176,16 +6177,16 @@
     </row>
     <row r="37" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B37" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C37" t="s">
         <v>43</v>
       </c>
       <c r="D37" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E37" t="s">
         <v>45</v>
@@ -6194,7 +6195,7 @@
         <v>46</v>
       </c>
       <c r="G37" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H37" t="s">
         <v>48</v>
@@ -6206,7 +6207,7 @@
         <v>145.4</v>
       </c>
       <c r="K37" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="L37">
         <v>13</v>
@@ -6236,37 +6237,37 @@
         <v>0.75300385848378304</v>
       </c>
       <c r="U37" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="W37" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="X37" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="Y37" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="Z37" t="s">
         <v>43</v>
       </c>
       <c r="AA37" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="AB37" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC37" t="s">
         <v>52</v>
       </c>
       <c r="AD37" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE37" t="s">
         <v>65</v>
       </c>
-      <c r="AE37" t="s">
-        <v>66</v>
-      </c>
       <c r="AG37" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="AH37">
         <v>9337</v>
@@ -6275,13 +6276,13 @@
         <v>9337</v>
       </c>
       <c r="AJ37" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK37">
         <v>70.08</v>
       </c>
       <c r="AL37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM37" t="s">
         <v>45</v>
@@ -6298,16 +6299,16 @@
     </row>
     <row r="38" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B38" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C38" t="s">
         <v>43</v>
       </c>
       <c r="D38" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E38" t="s">
         <v>45</v>
@@ -6316,7 +6317,7 @@
         <v>46</v>
       </c>
       <c r="G38" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s">
         <v>48</v>
@@ -6328,7 +6329,7 @@
         <v>145.4</v>
       </c>
       <c r="K38" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="L38">
         <v>13</v>
@@ -6358,37 +6359,37 @@
         <v>0.80103299449607501</v>
       </c>
       <c r="U38" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="W38" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="X38" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="Y38" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="Z38" t="s">
         <v>43</v>
       </c>
       <c r="AA38" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="AB38" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC38" t="s">
         <v>52</v>
       </c>
       <c r="AD38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE38" t="s">
         <v>54</v>
       </c>
       <c r="AG38" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="AH38">
         <v>9337</v>
@@ -6397,13 +6398,13 @@
         <v>9337</v>
       </c>
       <c r="AJ38" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK38">
         <v>69.08</v>
       </c>
       <c r="AL38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM38" t="s">
         <v>45</v>
@@ -6420,16 +6421,16 @@
     </row>
     <row r="39" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B39" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="C39" t="s">
         <v>43</v>
       </c>
       <c r="D39" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E39" t="s">
         <v>45</v>
@@ -6438,7 +6439,7 @@
         <v>46</v>
       </c>
       <c r="G39" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H39" t="s">
         <v>48</v>
@@ -6450,7 +6451,7 @@
         <v>145.4</v>
       </c>
       <c r="K39" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="L39">
         <v>13</v>
@@ -6480,37 +6481,37 @@
         <v>0.79748544035073399</v>
       </c>
       <c r="U39" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="W39" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="X39" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="Y39" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="Z39" t="s">
         <v>43</v>
       </c>
       <c r="AA39" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="AB39" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC39" t="s">
         <v>52</v>
       </c>
       <c r="AD39" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE39" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AG39" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="AH39">
         <v>9337</v>
@@ -6519,13 +6520,13 @@
         <v>9337</v>
       </c>
       <c r="AJ39" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK39">
         <v>77.2</v>
       </c>
       <c r="AL39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM39" t="s">
         <v>45</v>
@@ -6542,16 +6543,16 @@
     </row>
     <row r="40" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B40" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C40" t="s">
         <v>43</v>
       </c>
       <c r="D40" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E40" t="s">
         <v>45</v>
@@ -6572,7 +6573,7 @@
         <v>148.28</v>
       </c>
       <c r="K40" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="L40">
         <v>14</v>
@@ -6602,31 +6603,31 @@
         <v>0.84676897363794201</v>
       </c>
       <c r="U40" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="W40" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="X40" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="Y40" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="Z40" t="s">
         <v>43</v>
       </c>
       <c r="AA40" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="AB40" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC40" t="s">
         <v>52</v>
       </c>
       <c r="AD40" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE40" t="s">
         <v>54</v>
@@ -6635,7 +6636,7 @@
         <v>3425</v>
       </c>
       <c r="AG40" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="AH40">
         <v>9337</v>
@@ -6644,13 +6645,13 @@
         <v>9337</v>
       </c>
       <c r="AJ40" t="s">
-        <v>111</v>
+        <v>433</v>
       </c>
       <c r="AK40">
         <v>71.930000000000007</v>
       </c>
       <c r="AL40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM40" t="s">
         <v>45</v>
@@ -6667,16 +6668,16 @@
     </row>
     <row r="41" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B41" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C41" t="s">
         <v>43</v>
       </c>
       <c r="D41" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E41" t="s">
         <v>45</v>
@@ -6697,7 +6698,7 @@
         <v>148.28</v>
       </c>
       <c r="K41" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="L41">
         <v>14</v>
@@ -6727,31 +6728,31 @@
         <v>0.84234815122382301</v>
       </c>
       <c r="U41" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="W41" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="X41" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="Y41" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="Z41" t="s">
         <v>43</v>
       </c>
       <c r="AA41" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="AB41" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC41" t="s">
         <v>52</v>
       </c>
       <c r="AD41" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE41" t="s">
         <v>54</v>
@@ -6760,7 +6761,7 @@
         <v>3590</v>
       </c>
       <c r="AG41" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="AH41">
         <v>9337</v>
@@ -6769,13 +6770,13 @@
         <v>9337</v>
       </c>
       <c r="AJ41" t="s">
-        <v>111</v>
+        <v>433</v>
       </c>
       <c r="AK41">
         <v>69.150000000000006</v>
       </c>
       <c r="AL41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM41" t="s">
         <v>45</v>
@@ -6792,16 +6793,16 @@
     </row>
     <row r="42" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B42" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C42" t="s">
         <v>43</v>
       </c>
       <c r="D42" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E42" t="s">
         <v>45</v>
@@ -6822,7 +6823,7 @@
         <v>148.28</v>
       </c>
       <c r="K42" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="L42">
         <v>14</v>
@@ -6852,31 +6853,31 @@
         <v>0.85151244467685505</v>
       </c>
       <c r="U42" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="W42" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="X42" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="Y42" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="Z42" t="s">
         <v>43</v>
       </c>
       <c r="AA42" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="AB42" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AC42" t="s">
         <v>52</v>
       </c>
       <c r="AD42" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE42" t="s">
         <v>54</v>
@@ -6885,7 +6886,7 @@
         <v>3068</v>
       </c>
       <c r="AG42" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AH42">
         <v>9337</v>
@@ -6894,13 +6895,13 @@
         <v>9337</v>
       </c>
       <c r="AJ42" t="s">
-        <v>111</v>
+        <v>433</v>
       </c>
       <c r="AK42">
         <v>71.819999999999993</v>
       </c>
       <c r="AL42" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM42" t="s">
         <v>45</v>
@@ -6917,16 +6918,16 @@
     </row>
     <row r="43" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="B43" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="C43" t="s">
         <v>43</v>
       </c>
       <c r="D43" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E43" t="s">
         <v>45</v>
@@ -6947,7 +6948,7 @@
         <v>148.24</v>
       </c>
       <c r="K43" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="L43">
         <v>15</v>
@@ -6977,31 +6978,31 @@
         <v>0.90120443214175106</v>
       </c>
       <c r="U43" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="W43" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="X43" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="Y43" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="Z43" t="s">
         <v>43</v>
       </c>
       <c r="AA43" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="AB43" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC43" t="s">
         <v>52</v>
       </c>
       <c r="AD43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE43" t="s">
         <v>54</v>
@@ -7010,7 +7011,7 @@
         <v>3045</v>
       </c>
       <c r="AG43" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="AH43">
         <v>9337</v>
@@ -7019,13 +7020,13 @@
         <v>9337</v>
       </c>
       <c r="AJ43" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK43">
         <v>77.06</v>
       </c>
       <c r="AL43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM43" t="s">
         <v>45</v>
@@ -7042,16 +7043,16 @@
     </row>
     <row r="44" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B44" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C44" t="s">
         <v>43</v>
       </c>
       <c r="D44" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E44" t="s">
         <v>45</v>
@@ -7060,7 +7061,7 @@
         <v>46</v>
       </c>
       <c r="G44" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H44" t="s">
         <v>48</v>
@@ -7072,7 +7073,7 @@
         <v>147.12</v>
       </c>
       <c r="K44" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="L44">
         <v>16</v>
@@ -7102,40 +7103,40 @@
         <v>0.81327941961280004</v>
       </c>
       <c r="U44" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="W44" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="X44" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="Y44" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="Z44" t="s">
         <v>43</v>
       </c>
       <c r="AA44" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="AB44" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC44" t="s">
         <v>52</v>
       </c>
       <c r="AD44" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE44" t="s">
         <v>65</v>
-      </c>
-      <c r="AE44" t="s">
-        <v>66</v>
       </c>
       <c r="AF44">
         <v>1820</v>
       </c>
       <c r="AG44" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="AH44">
         <v>9337</v>
@@ -7144,13 +7145,13 @@
         <v>9337</v>
       </c>
       <c r="AJ44" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK44">
         <v>76.56</v>
       </c>
       <c r="AL44" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM44" t="s">
         <v>45</v>
@@ -7167,16 +7168,16 @@
     </row>
     <row r="45" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B45" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C45" t="s">
         <v>43</v>
       </c>
       <c r="D45" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E45" t="s">
         <v>45</v>
@@ -7185,7 +7186,7 @@
         <v>46</v>
       </c>
       <c r="G45" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H45" t="s">
         <v>48</v>
@@ -7197,7 +7198,7 @@
         <v>146.24</v>
       </c>
       <c r="K45" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="L45">
         <v>17</v>
@@ -7227,31 +7228,31 @@
         <v>0.79604732544638901</v>
       </c>
       <c r="U45" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="W45" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="X45" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="Y45" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="Z45" t="s">
         <v>43</v>
       </c>
       <c r="AA45" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="AB45" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC45" t="s">
         <v>52</v>
       </c>
       <c r="AD45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE45" t="s">
         <v>54</v>
@@ -7260,7 +7261,7 @@
         <v>4100</v>
       </c>
       <c r="AG45" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="AH45">
         <v>9337</v>
@@ -7269,13 +7270,13 @@
         <v>9337</v>
       </c>
       <c r="AJ45" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK45">
         <v>54.21</v>
       </c>
       <c r="AL45" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM45" t="s">
         <v>45</v>
@@ -7292,16 +7293,16 @@
     </row>
     <row r="46" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B46" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C46" t="s">
         <v>43</v>
       </c>
       <c r="D46" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E46" t="s">
         <v>45</v>
@@ -7322,7 +7323,7 @@
         <v>146.24</v>
       </c>
       <c r="K46" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="L46">
         <v>17</v>
@@ -7352,31 +7353,31 @@
         <v>0.80970895808097998</v>
       </c>
       <c r="U46" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="W46" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="X46" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="Y46" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="Z46" t="s">
         <v>43</v>
       </c>
       <c r="AA46" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="AB46" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AC46" t="s">
         <v>52</v>
       </c>
       <c r="AD46" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE46" t="s">
         <v>54</v>
@@ -7385,7 +7386,7 @@
         <v>3700</v>
       </c>
       <c r="AG46" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="AH46">
         <v>9337</v>
@@ -7394,13 +7395,13 @@
         <v>9337</v>
       </c>
       <c r="AJ46" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK46">
         <v>64.47</v>
       </c>
       <c r="AL46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM46" t="s">
         <v>45</v>
@@ -7417,16 +7418,16 @@
     </row>
     <row r="47" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B47" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C47" t="s">
         <v>43</v>
       </c>
       <c r="D47" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E47" t="s">
         <v>45</v>
@@ -7447,7 +7448,7 @@
         <v>146.24</v>
       </c>
       <c r="K47" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="L47">
         <v>17</v>
@@ -7477,31 +7478,31 @@
         <v>0.761917616000373</v>
       </c>
       <c r="U47" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="W47" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="X47" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="Y47" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="Z47" t="s">
         <v>43</v>
       </c>
       <c r="AA47" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="AB47" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AC47" t="s">
         <v>52</v>
       </c>
       <c r="AD47" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE47" t="s">
         <v>54</v>
@@ -7510,7 +7511,7 @@
         <v>3400</v>
       </c>
       <c r="AG47" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="AH47">
         <v>9337</v>
@@ -7519,13 +7520,13 @@
         <v>9337</v>
       </c>
       <c r="AJ47" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK47">
         <v>66.55</v>
       </c>
       <c r="AL47" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM47" t="s">
         <v>45</v>
@@ -7542,16 +7543,16 @@
     </row>
     <row r="48" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B48" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C48" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D48" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E48" t="s">
         <v>45</v>
@@ -7560,7 +7561,7 @@
         <v>46</v>
       </c>
       <c r="G48" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H48" t="s">
         <v>48</v>
@@ -7572,7 +7573,7 @@
         <v>116.96</v>
       </c>
       <c r="K48" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="L48">
         <v>18</v>
@@ -7602,22 +7603,22 @@
         <v>0.901093659865426</v>
       </c>
       <c r="U48" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="W48" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="X48" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="Y48" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="Z48" t="s">
         <v>43</v>
       </c>
       <c r="AA48" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="AB48" t="s">
         <v>51</v>
@@ -7632,7 +7633,7 @@
         <v>54</v>
       </c>
       <c r="AG48" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="AH48">
         <v>9337</v>
@@ -7641,13 +7642,13 @@
         <v>9337</v>
       </c>
       <c r="AJ48" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK48">
         <v>96.7</v>
       </c>
       <c r="AL48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM48" t="s">
         <v>45</v>
@@ -7664,16 +7665,16 @@
     </row>
     <row r="49" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B49" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C49" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D49" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E49" t="s">
         <v>45</v>
@@ -7682,7 +7683,7 @@
         <v>46</v>
       </c>
       <c r="G49" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H49" t="s">
         <v>48</v>
@@ -7694,7 +7695,7 @@
         <v>116.96</v>
       </c>
       <c r="K49" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="L49">
         <v>18</v>
@@ -7724,22 +7725,22 @@
         <v>0.88778240040597001</v>
       </c>
       <c r="U49" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="W49" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="X49" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="Y49" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="Z49" t="s">
         <v>43</v>
       </c>
       <c r="AA49" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="AB49" t="s">
         <v>51</v>
@@ -7754,7 +7755,7 @@
         <v>54</v>
       </c>
       <c r="AG49" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="AH49">
         <v>9337</v>
@@ -7763,13 +7764,13 @@
         <v>9337</v>
       </c>
       <c r="AJ49" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK49">
         <v>84.01</v>
       </c>
       <c r="AL49" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM49" t="s">
         <v>45</v>
@@ -7786,16 +7787,16 @@
     </row>
     <row r="50" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B50" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C50" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D50" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E50" t="s">
         <v>45</v>
@@ -7816,7 +7817,7 @@
         <v>116.47</v>
       </c>
       <c r="K50" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="L50">
         <v>19</v>
@@ -7846,28 +7847,28 @@
         <v>0.834838898</v>
       </c>
       <c r="U50" t="s">
+        <v>190</v>
+      </c>
+      <c r="V50" t="s">
+        <v>192</v>
+      </c>
+      <c r="W50" t="s">
+        <v>190</v>
+      </c>
+      <c r="X50" t="s">
+        <v>193</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>194</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>191</v>
+      </c>
+      <c r="AB50" t="s">
         <v>195</v>
-      </c>
-      <c r="V50" t="s">
-        <v>197</v>
-      </c>
-      <c r="W50" t="s">
-        <v>195</v>
-      </c>
-      <c r="X50" t="s">
-        <v>198</v>
-      </c>
-      <c r="Y50" t="s">
-        <v>199</v>
-      </c>
-      <c r="Z50" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA50" t="s">
-        <v>196</v>
-      </c>
-      <c r="AB50" t="s">
-        <v>200</v>
       </c>
       <c r="AC50" t="s">
         <v>52</v>
@@ -7882,7 +7883,7 @@
         <v>1830</v>
       </c>
       <c r="AG50" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="AH50">
         <v>9337</v>
@@ -7891,13 +7892,13 @@
         <v>9337</v>
       </c>
       <c r="AJ50" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK50">
         <v>85.06</v>
       </c>
       <c r="AL50" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM50" t="s">
         <v>45</v>
@@ -7914,16 +7915,16 @@
     </row>
     <row r="51" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B51" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C51" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D51" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E51" t="s">
         <v>45</v>
@@ -7944,7 +7945,7 @@
         <v>116.47</v>
       </c>
       <c r="K51" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="L51">
         <v>19</v>
@@ -7974,28 +7975,28 @@
         <v>0.90896454699999996</v>
       </c>
       <c r="U51" t="s">
+        <v>190</v>
+      </c>
+      <c r="V51" t="s">
+        <v>192</v>
+      </c>
+      <c r="W51" t="s">
+        <v>190</v>
+      </c>
+      <c r="X51" t="s">
+        <v>193</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>194</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>191</v>
+      </c>
+      <c r="AB51" t="s">
         <v>195</v>
-      </c>
-      <c r="V51" t="s">
-        <v>197</v>
-      </c>
-      <c r="W51" t="s">
-        <v>195</v>
-      </c>
-      <c r="X51" t="s">
-        <v>198</v>
-      </c>
-      <c r="Y51" t="s">
-        <v>199</v>
-      </c>
-      <c r="Z51" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA51" t="s">
-        <v>196</v>
-      </c>
-      <c r="AB51" t="s">
-        <v>200</v>
       </c>
       <c r="AC51" t="s">
         <v>52</v>
@@ -8010,7 +8011,7 @@
         <v>1830</v>
       </c>
       <c r="AG51" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="AH51">
         <v>9337</v>
@@ -8019,13 +8020,13 @@
         <v>9337</v>
       </c>
       <c r="AJ51" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK51">
         <v>84.46</v>
       </c>
       <c r="AL51" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM51" t="s">
         <v>45</v>
@@ -8042,16 +8043,16 @@
     </row>
     <row r="52" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B52" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C52" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D52" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E52" t="s">
         <v>45</v>
@@ -8072,7 +8073,7 @@
         <v>116.47</v>
       </c>
       <c r="K52" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="L52">
         <v>19</v>
@@ -8102,22 +8103,22 @@
         <v>0.88839248420153105</v>
       </c>
       <c r="U52" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="W52" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="X52" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="Y52" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="Z52" t="s">
         <v>43</v>
       </c>
       <c r="AA52" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="AB52" t="s">
         <v>51</v>
@@ -8135,7 +8136,7 @@
         <v>1130</v>
       </c>
       <c r="AG52" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="AH52">
         <v>9337</v>
@@ -8144,13 +8145,13 @@
         <v>9337</v>
       </c>
       <c r="AJ52" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK52">
         <v>87.37</v>
       </c>
       <c r="AL52" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM52" t="s">
         <v>45</v>
@@ -8167,16 +8168,16 @@
     </row>
     <row r="53" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B53" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C53" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D53" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E53" t="s">
         <v>45</v>
@@ -8197,7 +8198,7 @@
         <v>116.47</v>
       </c>
       <c r="K53" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="L53">
         <v>19</v>
@@ -8227,28 +8228,28 @@
         <v>0.74172077000000003</v>
       </c>
       <c r="U53" t="s">
+        <v>190</v>
+      </c>
+      <c r="V53" t="s">
+        <v>192</v>
+      </c>
+      <c r="W53" t="s">
+        <v>190</v>
+      </c>
+      <c r="X53" t="s">
+        <v>193</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>194</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA53" t="s">
+        <v>191</v>
+      </c>
+      <c r="AB53" t="s">
         <v>195</v>
-      </c>
-      <c r="V53" t="s">
-        <v>197</v>
-      </c>
-      <c r="W53" t="s">
-        <v>195</v>
-      </c>
-      <c r="X53" t="s">
-        <v>198</v>
-      </c>
-      <c r="Y53" t="s">
-        <v>199</v>
-      </c>
-      <c r="Z53" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA53" t="s">
-        <v>196</v>
-      </c>
-      <c r="AB53" t="s">
-        <v>200</v>
       </c>
       <c r="AC53" t="s">
         <v>52</v>
@@ -8263,7 +8264,7 @@
         <v>1830</v>
       </c>
       <c r="AG53" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="AH53">
         <v>9337</v>
@@ -8272,13 +8273,13 @@
         <v>9337</v>
       </c>
       <c r="AJ53" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK53">
         <v>84.61</v>
       </c>
       <c r="AL53" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM53" t="s">
         <v>45</v>
@@ -8295,16 +8296,16 @@
     </row>
     <row r="54" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B54" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="C54" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D54" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E54" t="s">
         <v>45</v>
@@ -8325,7 +8326,7 @@
         <v>116.47</v>
       </c>
       <c r="K54" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="L54">
         <v>19</v>
@@ -8355,22 +8356,22 @@
         <v>0.89498997230728605</v>
       </c>
       <c r="U54" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="W54" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="X54" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="Y54" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="Z54" t="s">
         <v>43</v>
       </c>
       <c r="AA54" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="AB54" t="s">
         <v>51</v>
@@ -8388,7 +8389,7 @@
         <v>1830</v>
       </c>
       <c r="AG54" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="AH54">
         <v>9337</v>
@@ -8397,13 +8398,13 @@
         <v>9337</v>
       </c>
       <c r="AJ54" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK54">
         <v>90.81</v>
       </c>
       <c r="AL54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM54" t="s">
         <v>45</v>
@@ -8420,16 +8421,16 @@
     </row>
     <row r="55" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B55" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C55" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D55" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E55" t="s">
         <v>45</v>
@@ -8450,7 +8451,7 @@
         <v>116.47</v>
       </c>
       <c r="K55" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="L55">
         <v>19</v>
@@ -8480,28 +8481,28 @@
         <v>0.76559285399999999</v>
       </c>
       <c r="U55" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="V55" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="W55" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="X55" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="Y55" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="Z55" t="s">
         <v>43</v>
       </c>
       <c r="AA55" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="AB55" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="AC55" t="s">
         <v>52</v>
@@ -8516,7 +8517,7 @@
         <v>1730</v>
       </c>
       <c r="AG55" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="AH55">
         <v>9337</v>
@@ -8525,13 +8526,13 @@
         <v>9337</v>
       </c>
       <c r="AJ55" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK55">
         <v>74.010000000000005</v>
       </c>
       <c r="AL55" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM55" t="s">
         <v>45</v>
@@ -8548,16 +8549,16 @@
     </row>
     <row r="56" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B56" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C56" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D56" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E56" t="s">
         <v>45</v>
@@ -8578,7 +8579,7 @@
         <v>116.47</v>
       </c>
       <c r="K56" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="L56">
         <v>19</v>
@@ -8608,22 +8609,22 @@
         <v>0.79291811476687801</v>
       </c>
       <c r="U56" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="W56" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="X56" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="Y56" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="Z56" t="s">
         <v>43</v>
       </c>
       <c r="AA56" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="AB56" t="s">
         <v>51</v>
@@ -8641,7 +8642,7 @@
         <v>1750</v>
       </c>
       <c r="AG56" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="AH56">
         <v>9337</v>
@@ -8650,13 +8651,13 @@
         <v>9337</v>
       </c>
       <c r="AJ56" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK56">
         <v>81.47</v>
       </c>
       <c r="AL56" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM56" t="s">
         <v>45</v>
@@ -8673,16 +8674,16 @@
     </row>
     <row r="57" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B57" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C57" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D57" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E57" t="s">
         <v>45</v>
@@ -8703,7 +8704,7 @@
         <v>116.47</v>
       </c>
       <c r="K57" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="L57">
         <v>19</v>
@@ -8733,22 +8734,22 @@
         <v>0.83456926491515604</v>
       </c>
       <c r="U57" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="W57" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="X57" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="Y57" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="Z57" t="s">
         <v>43</v>
       </c>
       <c r="AA57" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="AB57" t="s">
         <v>51</v>
@@ -8766,7 +8767,7 @@
         <v>1100</v>
       </c>
       <c r="AG57" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="AH57">
         <v>9337</v>
@@ -8775,13 +8776,13 @@
         <v>9337</v>
       </c>
       <c r="AJ57" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK57">
         <v>83.72</v>
       </c>
       <c r="AL57" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM57" t="s">
         <v>45</v>
@@ -8798,16 +8799,16 @@
     </row>
     <row r="58" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="B58" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C58" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D58" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E58" t="s">
         <v>45</v>
@@ -8828,7 +8829,7 @@
         <v>116.47</v>
       </c>
       <c r="K58" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="L58">
         <v>19</v>
@@ -8858,22 +8859,22 @@
         <v>0.87691443674677705</v>
       </c>
       <c r="U58" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="W58" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="X58" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="Y58" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="Z58" t="s">
         <v>43</v>
       </c>
       <c r="AA58" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="AB58" t="s">
         <v>51</v>
@@ -8891,7 +8892,7 @@
         <v>0</v>
       </c>
       <c r="AG58" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="AH58">
         <v>9337</v>
@@ -8900,13 +8901,13 @@
         <v>9337</v>
       </c>
       <c r="AJ58" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
       <c r="AK58">
         <v>85.99</v>
       </c>
       <c r="AL58" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM58" t="s">
         <v>45</v>
@@ -8923,16 +8924,16 @@
     </row>
     <row r="59" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>68</v>
+      </c>
+      <c r="B59" t="s">
+        <v>69</v>
+      </c>
+      <c r="C59" t="s">
+        <v>43</v>
+      </c>
+      <c r="D59" t="s">
         <v>70</v>
-      </c>
-      <c r="B59" t="s">
-        <v>71</v>
-      </c>
-      <c r="C59" t="s">
-        <v>43</v>
-      </c>
-      <c r="D59" t="s">
-        <v>72</v>
       </c>
       <c r="E59" t="s">
         <v>45</v>
@@ -8941,7 +8942,7 @@
         <v>46</v>
       </c>
       <c r="G59" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H59" t="s">
         <v>48</v>
@@ -8953,7 +8954,7 @@
         <v>139.04</v>
       </c>
       <c r="K59" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L59">
         <v>19</v>
@@ -8983,22 +8984,22 @@
         <v>0.81222614705695595</v>
       </c>
       <c r="U59" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="W59" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="X59" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Y59" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Z59" t="s">
         <v>43</v>
       </c>
       <c r="AA59" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AB59" t="s">
         <v>51</v>
@@ -9013,7 +9014,7 @@
         <v>54</v>
       </c>
       <c r="AG59" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AH59">
         <v>9337</v>
@@ -9022,13 +9023,13 @@
         <v>9337</v>
       </c>
       <c r="AJ59" t="s">
-        <v>77</v>
+        <v>432</v>
       </c>
       <c r="AK59">
         <v>77.540000000000006</v>
       </c>
       <c r="AL59" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM59" t="s">
         <v>45</v>
@@ -9045,16 +9046,16 @@
     </row>
     <row r="60" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B60" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C60" t="s">
         <v>43</v>
       </c>
       <c r="D60" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E60" t="s">
         <v>45</v>
@@ -9063,7 +9064,7 @@
         <v>46</v>
       </c>
       <c r="G60" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H60" t="s">
         <v>48</v>
@@ -9075,7 +9076,7 @@
         <v>139.04</v>
       </c>
       <c r="K60" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L60">
         <v>19</v>
@@ -9105,22 +9106,22 @@
         <v>0.68675225660358097</v>
       </c>
       <c r="U60" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="W60" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="X60" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="Y60" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="Z60" t="s">
         <v>43</v>
       </c>
       <c r="AA60" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AB60" t="s">
         <v>51</v>
@@ -9135,7 +9136,7 @@
         <v>54</v>
       </c>
       <c r="AG60" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AH60">
         <v>9337</v>
@@ -9144,13 +9145,13 @@
         <v>9337</v>
       </c>
       <c r="AJ60" t="s">
-        <v>77</v>
+        <v>432</v>
       </c>
       <c r="AK60">
         <v>3.32</v>
       </c>
       <c r="AL60" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM60" t="s">
         <v>45</v>
@@ -9167,16 +9168,16 @@
     </row>
     <row r="61" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B61" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C61" t="s">
         <v>43</v>
       </c>
       <c r="D61" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E61" t="s">
         <v>45</v>
@@ -9185,7 +9186,7 @@
         <v>46</v>
       </c>
       <c r="G61" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H61" t="s">
         <v>48</v>
@@ -9197,7 +9198,7 @@
         <v>139.04</v>
       </c>
       <c r="K61" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L61">
         <v>19</v>
@@ -9227,22 +9228,22 @@
         <v>0.83947716512099602</v>
       </c>
       <c r="U61" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="W61" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="X61" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="Y61" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="Z61" t="s">
         <v>43</v>
       </c>
       <c r="AA61" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AB61" t="s">
         <v>51</v>
@@ -9257,7 +9258,7 @@
         <v>54</v>
       </c>
       <c r="AG61" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AH61">
         <v>9337</v>
@@ -9266,13 +9267,13 @@
         <v>9337</v>
       </c>
       <c r="AJ61" t="s">
-        <v>77</v>
+        <v>432</v>
       </c>
       <c r="AK61">
         <v>93.95</v>
       </c>
       <c r="AL61" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM61" t="s">
         <v>45</v>
@@ -9289,16 +9290,16 @@
     </row>
     <row r="62" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B62" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="C62" t="s">
         <v>43</v>
       </c>
       <c r="D62" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E62" t="s">
         <v>45</v>
@@ -9307,7 +9308,7 @@
         <v>46</v>
       </c>
       <c r="G62" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H62" t="s">
         <v>48</v>
@@ -9319,7 +9320,7 @@
         <v>139.04</v>
       </c>
       <c r="K62" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L62">
         <v>19</v>
@@ -9349,22 +9350,22 @@
         <v>0.85871109749670005</v>
       </c>
       <c r="U62" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="W62" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="X62" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="Y62" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="Z62" t="s">
         <v>43</v>
       </c>
       <c r="AA62" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AB62" t="s">
         <v>51</v>
@@ -9379,7 +9380,7 @@
         <v>54</v>
       </c>
       <c r="AG62" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AH62">
         <v>9337</v>
@@ -9388,13 +9389,13 @@
         <v>9337</v>
       </c>
       <c r="AJ62" t="s">
-        <v>77</v>
+        <v>432</v>
       </c>
       <c r="AK62">
         <v>95.87</v>
       </c>
       <c r="AL62" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM62" t="s">
         <v>45</v>
@@ -9411,16 +9412,16 @@
     </row>
     <row r="63" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B63" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="C63" t="s">
         <v>43</v>
       </c>
       <c r="D63" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E63" t="s">
         <v>45</v>
@@ -9429,7 +9430,7 @@
         <v>46</v>
       </c>
       <c r="G63" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H63" t="s">
         <v>48</v>
@@ -9441,7 +9442,7 @@
         <v>139.04</v>
       </c>
       <c r="K63" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L63">
         <v>19</v>
@@ -9471,22 +9472,22 @@
         <v>0.90015204384418401</v>
       </c>
       <c r="U63" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="W63" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="X63" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="Y63" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="Z63" t="s">
         <v>43</v>
       </c>
       <c r="AA63" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AB63" t="s">
         <v>51</v>
@@ -9501,7 +9502,7 @@
         <v>54</v>
       </c>
       <c r="AG63" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AH63">
         <v>9337</v>
@@ -9510,13 +9511,13 @@
         <v>9337</v>
       </c>
       <c r="AJ63" t="s">
-        <v>77</v>
+        <v>432</v>
       </c>
       <c r="AK63">
         <v>100</v>
       </c>
       <c r="AL63" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM63" t="s">
         <v>45</v>
@@ -9533,16 +9534,16 @@
     </row>
     <row r="64" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B64" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="C64" t="s">
         <v>43</v>
       </c>
       <c r="D64" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E64" t="s">
         <v>45</v>
@@ -9551,7 +9552,7 @@
         <v>46</v>
       </c>
       <c r="G64" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H64" t="s">
         <v>48</v>
@@ -9563,7 +9564,7 @@
         <v>139.04</v>
       </c>
       <c r="K64" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L64">
         <v>19</v>
@@ -9593,22 +9594,22 @@
         <v>0.85042658579175201</v>
       </c>
       <c r="U64" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="W64" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="X64" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="Y64" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="Z64" t="s">
         <v>43</v>
       </c>
       <c r="AA64" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AB64" t="s">
         <v>51</v>
@@ -9623,7 +9624,7 @@
         <v>54</v>
       </c>
       <c r="AG64" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AH64">
         <v>9337</v>
@@ -9632,13 +9633,13 @@
         <v>9337</v>
       </c>
       <c r="AJ64" t="s">
-        <v>77</v>
+        <v>432</v>
       </c>
       <c r="AK64">
         <v>88.97</v>
       </c>
       <c r="AL64" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM64" t="s">
         <v>45</v>
@@ -9655,16 +9656,16 @@
     </row>
     <row r="65" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="B65" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="C65" t="s">
         <v>43</v>
       </c>
       <c r="D65" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E65" t="s">
         <v>45</v>
@@ -9673,7 +9674,7 @@
         <v>46</v>
       </c>
       <c r="G65" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H65" t="s">
         <v>48</v>
@@ -9685,7 +9686,7 @@
         <v>139.04</v>
       </c>
       <c r="K65" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L65">
         <v>19</v>
@@ -9715,22 +9716,22 @@
         <v>0.86633956222899999</v>
       </c>
       <c r="U65" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="W65" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="X65" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="Y65" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="Z65" t="s">
         <v>43</v>
       </c>
       <c r="AA65" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AB65" t="s">
         <v>51</v>
@@ -9745,7 +9746,7 @@
         <v>54</v>
       </c>
       <c r="AG65" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AH65">
         <v>9337</v>
@@ -9754,13 +9755,13 @@
         <v>9337</v>
       </c>
       <c r="AJ65" t="s">
-        <v>77</v>
+        <v>432</v>
       </c>
       <c r="AK65">
         <v>89.07</v>
       </c>
       <c r="AL65" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM65" t="s">
         <v>45</v>
@@ -9777,10 +9778,10 @@
     </row>
     <row r="66" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B66" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C66" t="s">
         <v>43</v>
@@ -9795,7 +9796,7 @@
         <v>46</v>
       </c>
       <c r="G66" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H66" t="s">
         <v>48</v>
@@ -9807,7 +9808,7 @@
         <v>146.91</v>
       </c>
       <c r="K66" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L66">
         <v>20</v>
@@ -9837,16 +9838,16 @@
         <v>0.867479117626757</v>
       </c>
       <c r="U66" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="W66" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="X66" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="Y66" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Z66" t="s">
         <v>43</v>
@@ -9879,13 +9880,13 @@
         <v>9337</v>
       </c>
       <c r="AJ66" t="s">
-        <v>92</v>
+        <v>431</v>
       </c>
       <c r="AK66">
         <v>85.23</v>
       </c>
       <c r="AL66" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM66" t="s">
         <v>45</v>
@@ -9902,10 +9903,10 @@
     </row>
     <row r="67" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B67" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C67" t="s">
         <v>43</v>
@@ -9920,7 +9921,7 @@
         <v>46</v>
       </c>
       <c r="G67" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H67" t="s">
         <v>48</v>
@@ -9932,7 +9933,7 @@
         <v>146.91</v>
       </c>
       <c r="K67" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L67">
         <v>20</v>
@@ -9962,16 +9963,16 @@
         <v>0.88468515490071398</v>
       </c>
       <c r="U67" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="W67" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="X67" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="Y67" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Z67" t="s">
         <v>43</v>
@@ -10004,13 +10005,13 @@
         <v>9337</v>
       </c>
       <c r="AJ67" t="s">
-        <v>92</v>
+        <v>431</v>
       </c>
       <c r="AK67">
         <v>81.19</v>
       </c>
       <c r="AL67" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM67" t="s">
         <v>45</v>
@@ -10027,10 +10028,10 @@
     </row>
     <row r="68" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B68" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C68" t="s">
         <v>43</v>
@@ -10045,7 +10046,7 @@
         <v>46</v>
       </c>
       <c r="G68" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H68" t="s">
         <v>48</v>
@@ -10057,7 +10058,7 @@
         <v>146.91</v>
       </c>
       <c r="K68" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L68">
         <v>20</v>
@@ -10087,16 +10088,16 @@
         <v>0.88745885513931699</v>
       </c>
       <c r="U68" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="W68" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="X68" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="Y68" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="Z68" t="s">
         <v>43</v>
@@ -10120,7 +10121,7 @@
         <v>2940</v>
       </c>
       <c r="AG68" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="AH68">
         <v>9337</v>
@@ -10129,13 +10130,13 @@
         <v>9337</v>
       </c>
       <c r="AJ68" t="s">
-        <v>92</v>
+        <v>431</v>
       </c>
       <c r="AK68">
         <v>85.86</v>
       </c>
       <c r="AL68" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM68" t="s">
         <v>45</v>
@@ -10152,10 +10153,10 @@
     </row>
     <row r="69" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="B69" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="C69" t="s">
         <v>43</v>
@@ -10170,7 +10171,7 @@
         <v>46</v>
       </c>
       <c r="G69" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H69" t="s">
         <v>48</v>
@@ -10182,7 +10183,7 @@
         <v>146.91</v>
       </c>
       <c r="K69" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L69">
         <v>20</v>
@@ -10212,16 +10213,16 @@
         <v>0.86544078914070899</v>
       </c>
       <c r="U69" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="W69" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="X69" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="Y69" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="Z69" t="s">
         <v>43</v>
@@ -10245,7 +10246,7 @@
         <v>3920</v>
       </c>
       <c r="AG69" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="AH69">
         <v>9337</v>
@@ -10254,13 +10255,13 @@
         <v>9337</v>
       </c>
       <c r="AJ69" t="s">
-        <v>92</v>
+        <v>431</v>
       </c>
       <c r="AK69">
         <v>85.19</v>
       </c>
       <c r="AL69" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM69" t="s">
         <v>45</v>
@@ -10307,7 +10308,7 @@
         <v>147.02000000000001</v>
       </c>
       <c r="K70" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L70">
         <v>21</v>
@@ -10379,13 +10380,13 @@
         <v>9337</v>
       </c>
       <c r="AJ70" t="s">
-        <v>56</v>
+        <v>430</v>
       </c>
       <c r="AK70">
         <v>92.8</v>
       </c>
       <c r="AL70" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM70" t="s">
         <v>45</v>
@@ -10402,10 +10403,10 @@
     </row>
     <row r="71" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B71" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C71" t="s">
         <v>43</v>
@@ -10432,7 +10433,7 @@
         <v>147.02000000000001</v>
       </c>
       <c r="K71" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L71">
         <v>21</v>
@@ -10462,16 +10463,16 @@
         <v>0.93733184105854395</v>
       </c>
       <c r="U71" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="W71" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="X71" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="Y71" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="Z71" t="s">
         <v>43</v>
@@ -10495,7 +10496,7 @@
         <v>4020</v>
       </c>
       <c r="AG71" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="AH71">
         <v>9337</v>
@@ -10504,13 +10505,13 @@
         <v>9337</v>
       </c>
       <c r="AJ71" t="s">
-        <v>56</v>
+        <v>430</v>
       </c>
       <c r="AK71">
         <v>82.19</v>
       </c>
       <c r="AL71" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM71" t="s">
         <v>45</v>
@@ -10527,10 +10528,10 @@
     </row>
     <row r="72" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B72" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C72" t="s">
         <v>43</v>
@@ -10557,7 +10558,7 @@
         <v>147.02000000000001</v>
       </c>
       <c r="K72" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L72">
         <v>21</v>
@@ -10587,16 +10588,16 @@
         <v>0.89906260787932302</v>
       </c>
       <c r="U72" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="W72" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="X72" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="Y72" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="Z72" t="s">
         <v>43</v>
@@ -10620,7 +10621,7 @@
         <v>3850</v>
       </c>
       <c r="AG72" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="AH72">
         <v>9337</v>
@@ -10629,13 +10630,13 @@
         <v>9337</v>
       </c>
       <c r="AJ72" t="s">
-        <v>56</v>
+        <v>430</v>
       </c>
       <c r="AK72">
         <v>83.27</v>
       </c>
       <c r="AL72" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM72" t="s">
         <v>45</v>
@@ -10652,10 +10653,10 @@
     </row>
     <row r="73" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B73" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C73" t="s">
         <v>43</v>
@@ -10670,7 +10671,7 @@
         <v>46</v>
       </c>
       <c r="G73" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H73" t="s">
         <v>48</v>
@@ -10682,7 +10683,7 @@
         <v>147.02000000000001</v>
       </c>
       <c r="K73" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L73">
         <v>21</v>
@@ -10712,16 +10713,16 @@
         <v>0.97101000261485904</v>
       </c>
       <c r="U73" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="W73" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="X73" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="Y73" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="Z73" t="s">
         <v>43</v>
@@ -10745,7 +10746,7 @@
         <v>2690</v>
       </c>
       <c r="AG73" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="AH73">
         <v>9337</v>
@@ -10754,13 +10755,13 @@
         <v>9337</v>
       </c>
       <c r="AJ73" t="s">
-        <v>56</v>
+        <v>430</v>
       </c>
       <c r="AK73">
         <v>85.82</v>
       </c>
       <c r="AL73" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM73" t="s">
         <v>45</v>
@@ -10777,10 +10778,10 @@
     </row>
     <row r="74" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B74" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="C74" t="s">
         <v>43</v>
@@ -10795,7 +10796,7 @@
         <v>46</v>
       </c>
       <c r="G74" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H74" t="s">
         <v>48</v>
@@ -10807,7 +10808,7 @@
         <v>147.02000000000001</v>
       </c>
       <c r="K74" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L74">
         <v>21</v>
@@ -10837,16 +10838,16 @@
         <v>0.96934156561226903</v>
       </c>
       <c r="U74" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="W74" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="X74" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="Y74" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="Z74" t="s">
         <v>43</v>
@@ -10870,7 +10871,7 @@
         <v>2260</v>
       </c>
       <c r="AG74" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="AH74">
         <v>9337</v>
@@ -10879,13 +10880,13 @@
         <v>9337</v>
       </c>
       <c r="AJ74" t="s">
-        <v>56</v>
+        <v>430</v>
       </c>
       <c r="AK74">
         <v>100</v>
       </c>
       <c r="AL74" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AM74" t="s">
         <v>45</v>

--- a/sample_metadata.xlsx
+++ b/sample_metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lukas\Documents\GitHub\btp_metagenomics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{923C5BC5-AFFE-4617-9D00-A387E38240C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A873FD7F-B241-4235-9DD1-B5F5E80DA5D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2955" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1681,6 +1681,7 @@
     <col min="10" max="10" width="18.85546875" customWidth="1"/>
     <col min="11" max="11" width="88.5703125" customWidth="1"/>
     <col min="12" max="12" width="18.85546875" customWidth="1"/>
+    <col min="33" max="33" width="18" customWidth="1"/>
     <col min="36" max="36" width="31.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
